--- a/public/templates/Maitsys-Assure-Master-Requirement-Import-Template.xlsx
+++ b/public/templates/Maitsys-Assure-Master-Requirement-Import-Template.xlsx
@@ -1,39 +1,31 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
-  <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{834AF4EB-0A5D-49A6-BDDD-5C3C80D2AED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Instructions" sheetId="2" r:id="rId1"/>
-    <sheet name="Import Template" sheetId="1" r:id="rId2"/>
-    <sheet name="Sample Data" sheetId="4" r:id="rId3"/>
-    <sheet name="Lookup Lists" sheetId="3" r:id="rId4"/>
-  </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>Microsoft Excel Online</Application>
+  <Manager/>
+  <Company/>
+  <HyperlinkBase/>
+  <AppVersion>16.0300</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:title/>
+  <dc:subject/>
+  <dc:creator>openpyxl</dc:creator>
+  <cp:keywords/>
+  <dc:description/>
+  <cp:lastModifiedBy/>
+  <cp:revision/>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-09-02T10:26:29Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-09-02T11:00:05Z</dcterms:modified>
+  <cp:category/>
+  <cp:contentStatus/>
+</cp:coreProperties>
+</file>
+
+<file path=xl\comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Maitsys Assure</author>
@@ -99,7 +91,7 @@
 </comments>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="613">
   <si>
     <t>How to Fill In This Template</t>
@@ -183,7 +175,7 @@
     <t>Evidence Requirement</t>
   </si>
   <si>
-    <t>What the site must attach as proof for this specific question. If the source has more than one evidence item for the same question, put each on its own line inside the same cell (Alt+Enter in Excel).</t>
+    <t>What the site must attach as proof for this specific question. If the source has more than one evidence item for the same question, put each on its own line inside the same cell (Alt+Enter in Excel). For a Partial or Yes answer, the site must explain how each file or link they upload meets this requirement.</t>
   </si>
   <si>
     <t>Tiered accountability KPI’s are aligned with EHS&amp;S Standard. Include a picture and/or process description.</t>
@@ -1978,7 +1970,7 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="11">
     <font>
@@ -2160,7 +2152,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -2443,7 +2435,7 @@
 </a:theme>
 </file>
 
-<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\webextensions\taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
   <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2451,7 +2443,7 @@
 </wetp:taskpanes>
 </file>
 
-<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\webextensions\webextension1.xml><?xml version="1.0" encoding="utf-8"?>
 <we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{D7E14C31-846E-4622-A529-58AC112E4466}">
   <we:reference id="WA200009404" version="1.0.0.8" store="en-us" storeType="omex"/>
   <we:alternateReferences>
@@ -2470,7 +2462,41 @@
 </we:webextension>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
+  <workbookPr/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{834AF4EB-0A5D-49A6-BDDD-5C3C80D2AED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Instructions" sheetId="2" r:id="rId1"/>
+    <sheet name="Import Template" sheetId="1" r:id="rId2"/>
+    <sheet name="Sample Data" sheetId="4" r:id="rId3"/>
+    <sheet name="Lookup Lists" sheetId="3" r:id="rId4"/>
+  </sheets>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2592,7 +2618,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="42" customHeight="1">
+    <row r="11" spans="1:4" ht="56" customHeight="1">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
@@ -2682,20 +2708,6 @@
       </c>
       <c r="D17" s="11" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="42" customHeight="1">
-      <c r="A18" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2770,9 +2782,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -2786,20 +2798,19 @@
     <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:13">
       <c r="A2" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="30" customHeight="1">
+    <row r="4" spans="1:13" ht="30" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>52</v>
       </c>
@@ -2839,11 +2850,8 @@
       <c r="M4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="N4" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="5" spans="1:13" ht="45.95" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
@@ -2875,11 +2883,8 @@
       <c r="M5" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N5" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="6" spans="1:13" ht="45.95" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
@@ -2911,11 +2916,8 @@
       <c r="M6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N6" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="7" spans="1:13" ht="45.95" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -2947,11 +2949,8 @@
       <c r="M7" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N7" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="8" spans="1:13" ht="45.95" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>9</v>
       </c>
@@ -2983,11 +2982,8 @@
       <c r="M8" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N8" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="9" spans="1:13" ht="45.95" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>9</v>
       </c>
@@ -3019,11 +3015,8 @@
       <c r="M9" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N9" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="10" spans="1:13" ht="45.95" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
@@ -3055,11 +3048,8 @@
       <c r="M10" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N10" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="11" spans="1:13" ht="45.95" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
@@ -3091,11 +3081,8 @@
       <c r="M11" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N11" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="12" spans="1:13" ht="45.95" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>9</v>
       </c>
@@ -3127,11 +3114,8 @@
       <c r="M12" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N12" s="5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="13" spans="1:13" ht="45.95" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>9</v>
       </c>
@@ -3163,11 +3147,8 @@
       <c r="M13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N13" s="5">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="14" spans="1:13" ht="45.95" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>9</v>
       </c>
@@ -3199,11 +3180,8 @@
       <c r="M14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N14" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="15" spans="1:13" ht="45.95" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>9</v>
       </c>
@@ -3235,11 +3213,8 @@
       <c r="M15" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N15" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="16" spans="1:13" ht="45.95" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>9</v>
       </c>
@@ -3271,11 +3246,8 @@
       <c r="M16" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N16" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="17" spans="1:13" ht="45.95" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>9</v>
       </c>
@@ -3307,11 +3279,8 @@
       <c r="M17" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N17" s="5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="18" spans="1:13" ht="45.95" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>9</v>
       </c>
@@ -3343,11 +3312,8 @@
       <c r="M18" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N18" s="5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="19" spans="1:13" ht="45.95" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>9</v>
       </c>
@@ -3379,11 +3345,8 @@
       <c r="M19" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N19" s="5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="20" spans="1:13" ht="45.95" customHeight="1">
       <c r="A20" s="4" t="s">
         <v>9</v>
       </c>
@@ -3415,11 +3378,8 @@
       <c r="M20" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N20" s="5">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="21" spans="1:13" ht="45.95" customHeight="1">
       <c r="A21" s="4" t="s">
         <v>9</v>
       </c>
@@ -3451,11 +3411,8 @@
       <c r="M21" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N21" s="5">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="22" spans="1:13" ht="45.95" customHeight="1">
       <c r="A22" s="4" t="s">
         <v>9</v>
       </c>
@@ -3487,11 +3444,8 @@
       <c r="M22" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N22" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="23" spans="1:13" ht="45.95" customHeight="1">
       <c r="A23" s="4" t="s">
         <v>9</v>
       </c>
@@ -3523,11 +3477,8 @@
       <c r="M23" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N23" s="5">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="24" spans="1:13" ht="45.95" customHeight="1">
       <c r="A24" s="4" t="s">
         <v>9</v>
       </c>
@@ -3559,11 +3510,8 @@
       <c r="M24" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N24" s="5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="25" spans="1:13" ht="45.95" customHeight="1">
       <c r="A25" s="4" t="s">
         <v>9</v>
       </c>
@@ -3595,11 +3543,8 @@
       <c r="M25" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N25" s="5">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="26" spans="1:13" ht="45.95" customHeight="1">
       <c r="A26" s="4" t="s">
         <v>9</v>
       </c>
@@ -3631,11 +3576,8 @@
       <c r="M26" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N26" s="5">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="27" spans="1:13" ht="45.95" customHeight="1">
       <c r="A27" s="4" t="s">
         <v>9</v>
       </c>
@@ -3667,11 +3609,8 @@
       <c r="M27" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N27" s="5">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="28" spans="1:13" ht="45.95" customHeight="1">
       <c r="A28" s="4" t="s">
         <v>9</v>
       </c>
@@ -3703,11 +3642,8 @@
       <c r="M28" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N28" s="5">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="29" spans="1:13" ht="45.95" customHeight="1">
       <c r="A29" s="4" t="s">
         <v>9</v>
       </c>
@@ -3739,11 +3675,8 @@
       <c r="M29" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N29" s="5">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="30" spans="1:13" ht="45.95" customHeight="1">
       <c r="A30" s="4" t="s">
         <v>9</v>
       </c>
@@ -3775,11 +3708,8 @@
       <c r="M30" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N30" s="5">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="31" spans="1:13" ht="45.95" customHeight="1">
       <c r="A31" s="4" t="s">
         <v>9</v>
       </c>
@@ -3811,11 +3741,8 @@
       <c r="M31" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N31" s="5">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="32" spans="1:13" ht="45.95" customHeight="1">
       <c r="A32" s="4" t="s">
         <v>9</v>
       </c>
@@ -3847,11 +3774,8 @@
       <c r="M32" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N32" s="5">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="33" spans="1:13" ht="45.95" customHeight="1">
       <c r="A33" s="4" t="s">
         <v>9</v>
       </c>
@@ -3883,11 +3807,8 @@
       <c r="M33" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N33" s="5">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="34" spans="1:13" ht="45.95" customHeight="1">
       <c r="A34" s="4" t="s">
         <v>9</v>
       </c>
@@ -3919,11 +3840,8 @@
       <c r="M34" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N34" s="5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="35" spans="1:13" ht="45.95" customHeight="1">
       <c r="A35" s="4" t="s">
         <v>9</v>
       </c>
@@ -3955,11 +3873,8 @@
       <c r="M35" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N35" s="5">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="36" spans="1:13" ht="45.95" customHeight="1">
       <c r="A36" s="4" t="s">
         <v>9</v>
       </c>
@@ -3991,11 +3906,8 @@
       <c r="M36" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N36" s="5">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="37" spans="1:13" ht="45.95" customHeight="1">
       <c r="A37" s="4" t="s">
         <v>9</v>
       </c>
@@ -4027,11 +3939,8 @@
       <c r="M37" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N37" s="5">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="38" spans="1:13" ht="45.95" customHeight="1">
       <c r="A38" s="4" t="s">
         <v>9</v>
       </c>
@@ -4063,11 +3972,8 @@
       <c r="M38" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N38" s="5">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="39" spans="1:13" ht="45.95" customHeight="1">
       <c r="A39" s="4" t="s">
         <v>9</v>
       </c>
@@ -4099,11 +4005,8 @@
       <c r="M39" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N39" s="5">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="40" spans="1:13" ht="45.95" customHeight="1">
       <c r="A40" s="4" t="s">
         <v>9</v>
       </c>
@@ -4135,11 +4038,8 @@
       <c r="M40" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N40" s="5">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="41" spans="1:13" ht="45.95" customHeight="1">
       <c r="A41" s="4" t="s">
         <v>9</v>
       </c>
@@ -4171,11 +4071,8 @@
       <c r="M41" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N41" s="5">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="42" spans="1:13" ht="45.95" customHeight="1">
       <c r="A42" s="4" t="s">
         <v>9</v>
       </c>
@@ -4207,11 +4104,8 @@
       <c r="M42" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N42" s="5">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="43" spans="1:13" ht="45.95" customHeight="1">
       <c r="A43" s="4" t="s">
         <v>9</v>
       </c>
@@ -4243,11 +4137,8 @@
       <c r="M43" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N43" s="5">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="44" spans="1:13" ht="45.95" customHeight="1">
       <c r="A44" s="4" t="s">
         <v>9</v>
       </c>
@@ -4279,11 +4170,8 @@
       <c r="M44" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N44" s="5">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="45" spans="1:13" ht="45.95" customHeight="1">
       <c r="A45" s="4" t="s">
         <v>9</v>
       </c>
@@ -4315,11 +4203,8 @@
       <c r="M45" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N45" s="5">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="46" spans="1:13" ht="45.95" customHeight="1">
       <c r="A46" s="4" t="s">
         <v>9</v>
       </c>
@@ -4351,11 +4236,8 @@
       <c r="M46" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N46" s="5">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="47" spans="1:13" ht="45.95" customHeight="1">
       <c r="A47" s="4" t="s">
         <v>9</v>
       </c>
@@ -4387,11 +4269,8 @@
       <c r="M47" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N47" s="5">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="48" spans="1:13" ht="45.95" customHeight="1">
       <c r="A48" s="4" t="s">
         <v>9</v>
       </c>
@@ -4423,11 +4302,8 @@
       <c r="M48" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N48" s="5">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="49" spans="1:13" ht="45.95" customHeight="1">
       <c r="A49" s="4" t="s">
         <v>9</v>
       </c>
@@ -4459,11 +4335,8 @@
       <c r="M49" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N49" s="5">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" ht="45.95" customHeight="1">
+    </row>
+    <row r="50" spans="1:13" ht="45.95" customHeight="1">
       <c r="A50" s="4" t="s">
         <v>9</v>
       </c>
@@ -4495,11 +4368,8 @@
       <c r="M50" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N50" s="5">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14">
+    </row>
+    <row r="51" spans="1:13">
       <c r="A51" s="6" t="s">
         <v>234</v>
       </c>
@@ -4533,11 +4403,8 @@
       <c r="M51" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="N51" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14">
+    </row>
+    <row r="52" spans="1:13">
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="9"/>
@@ -4551,9 +4418,8 @@
       <c r="K52" s="9"/>
       <c r="L52" s="9"/>
       <c r="M52" s="9"/>
-      <c r="N52" s="9"/>
-    </row>
-    <row r="53" spans="1:14">
+    </row>
+    <row r="53" spans="1:13">
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="9"/>
@@ -4567,9 +4433,8 @@
       <c r="K53" s="9"/>
       <c r="L53" s="9"/>
       <c r="M53" s="9"/>
-      <c r="N53" s="9"/>
-    </row>
-    <row r="54" spans="1:14">
+    </row>
+    <row r="54" spans="1:13">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="9"/>
@@ -4583,9 +4448,8 @@
       <c r="K54" s="9"/>
       <c r="L54" s="9"/>
       <c r="M54" s="9"/>
-      <c r="N54" s="9"/>
-    </row>
-    <row r="55" spans="1:14">
+    </row>
+    <row r="55" spans="1:13">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="9"/>
@@ -4599,9 +4463,8 @@
       <c r="K55" s="9"/>
       <c r="L55" s="9"/>
       <c r="M55" s="9"/>
-      <c r="N55" s="9"/>
-    </row>
-    <row r="56" spans="1:14">
+    </row>
+    <row r="56" spans="1:13">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="9"/>
@@ -4615,9 +4478,8 @@
       <c r="K56" s="9"/>
       <c r="L56" s="9"/>
       <c r="M56" s="9"/>
-      <c r="N56" s="9"/>
-    </row>
-    <row r="57" spans="1:14">
+    </row>
+    <row r="57" spans="1:13">
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="9"/>
@@ -4631,9 +4493,8 @@
       <c r="K57" s="9"/>
       <c r="L57" s="9"/>
       <c r="M57" s="9"/>
-      <c r="N57" s="9"/>
-    </row>
-    <row r="58" spans="1:14">
+    </row>
+    <row r="58" spans="1:13">
       <c r="A58" s="8"/>
       <c r="B58" s="8"/>
       <c r="C58" s="9"/>
@@ -4647,7 +4508,6 @@
       <c r="K58" s="9"/>
       <c r="L58" s="9"/>
       <c r="M58" s="9"/>
-      <c r="N58" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -4672,9 +4532,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:N104"/>
+  <dimension ref="A1:M104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -4688,20 +4548,19 @@
     <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:13">
       <c r="A2" s="2" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="30" customHeight="1">
+    <row r="4" spans="1:13" ht="30" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>52</v>
       </c>
@@ -4741,11 +4600,8 @@
       <c r="M4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="N4" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="5" spans="1:13" ht="44.1" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>244</v>
       </c>
@@ -4777,11 +4633,8 @@
       <c r="M5" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N5" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="6" spans="1:13" ht="44.1" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>244</v>
       </c>
@@ -4813,11 +4666,8 @@
       <c r="M6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N6" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="7" spans="1:13" ht="44.1" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>244</v>
       </c>
@@ -4849,11 +4699,8 @@
       <c r="M7" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N7" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="8" spans="1:13" ht="44.1" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>244</v>
       </c>
@@ -4885,11 +4732,8 @@
       <c r="M8" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N8" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="9" spans="1:13" ht="44.1" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>244</v>
       </c>
@@ -4921,11 +4765,8 @@
       <c r="M9" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N9" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="10" spans="1:13" ht="44.1" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>244</v>
       </c>
@@ -4957,11 +4798,8 @@
       <c r="M10" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N10" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="11" spans="1:13" ht="44.1" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>244</v>
       </c>
@@ -4993,11 +4831,8 @@
       <c r="M11" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N11" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="12" spans="1:13" ht="44.1" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>244</v>
       </c>
@@ -5029,11 +4864,8 @@
       <c r="M12" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N12" s="5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="13" spans="1:13" ht="44.1" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>244</v>
       </c>
@@ -5065,11 +4897,8 @@
       <c r="M13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N13" s="5">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="14" spans="1:13" ht="44.1" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>244</v>
       </c>
@@ -5101,11 +4930,8 @@
       <c r="M14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N14" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="15" spans="1:13" ht="44.1" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>244</v>
       </c>
@@ -5137,11 +4963,8 @@
       <c r="M15" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N15" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="16" spans="1:13" ht="44.1" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>244</v>
       </c>
@@ -5173,11 +4996,8 @@
       <c r="M16" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N16" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="17" spans="1:13" ht="44.1" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>244</v>
       </c>
@@ -5209,11 +5029,8 @@
       <c r="M17" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N17" s="5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="18" spans="1:13" ht="44.1" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>244</v>
       </c>
@@ -5245,11 +5062,8 @@
       <c r="M18" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N18" s="5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="19" spans="1:13" ht="44.1" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>244</v>
       </c>
@@ -5281,11 +5095,8 @@
       <c r="M19" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N19" s="5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="20" spans="1:13" ht="44.1" customHeight="1">
       <c r="A20" s="4" t="s">
         <v>244</v>
       </c>
@@ -5317,11 +5128,8 @@
       <c r="M20" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N20" s="5">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="21" spans="1:13" ht="44.1" customHeight="1">
       <c r="A21" s="4" t="s">
         <v>244</v>
       </c>
@@ -5353,11 +5161,8 @@
       <c r="M21" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N21" s="5">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="22" spans="1:13" ht="44.1" customHeight="1">
       <c r="A22" s="4" t="s">
         <v>244</v>
       </c>
@@ -5389,11 +5194,8 @@
       <c r="M22" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N22" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="23" spans="1:13" ht="44.1" customHeight="1">
       <c r="A23" s="4" t="s">
         <v>244</v>
       </c>
@@ -5425,11 +5227,8 @@
       <c r="M23" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N23" s="5">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="24" spans="1:13" ht="44.1" customHeight="1">
       <c r="A24" s="4" t="s">
         <v>244</v>
       </c>
@@ -5461,11 +5260,8 @@
       <c r="M24" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N24" s="5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="25" spans="1:13" ht="44.1" customHeight="1">
       <c r="A25" s="4" t="s">
         <v>317</v>
       </c>
@@ -5497,11 +5293,8 @@
       <c r="M25" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N25" s="5">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="26" spans="1:13" ht="44.1" customHeight="1">
       <c r="A26" s="4" t="s">
         <v>317</v>
       </c>
@@ -5533,11 +5326,8 @@
       <c r="M26" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N26" s="5">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="27" spans="1:13" ht="44.1" customHeight="1">
       <c r="A27" s="4" t="s">
         <v>317</v>
       </c>
@@ -5569,11 +5359,8 @@
       <c r="M27" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N27" s="5">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="28" spans="1:13" ht="44.1" customHeight="1">
       <c r="A28" s="4" t="s">
         <v>317</v>
       </c>
@@ -5605,11 +5392,8 @@
       <c r="M28" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N28" s="5">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="29" spans="1:13" ht="44.1" customHeight="1">
       <c r="A29" s="4" t="s">
         <v>317</v>
       </c>
@@ -5641,11 +5425,8 @@
       <c r="M29" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N29" s="5">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="30" spans="1:13" ht="44.1" customHeight="1">
       <c r="A30" s="4" t="s">
         <v>317</v>
       </c>
@@ -5677,11 +5458,8 @@
       <c r="M30" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N30" s="5">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="31" spans="1:13" ht="44.1" customHeight="1">
       <c r="A31" s="4" t="s">
         <v>317</v>
       </c>
@@ -5713,11 +5491,8 @@
       <c r="M31" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N31" s="5">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="32" spans="1:13" ht="44.1" customHeight="1">
       <c r="A32" s="4" t="s">
         <v>317</v>
       </c>
@@ -5749,11 +5524,8 @@
       <c r="M32" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N32" s="5">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="33" spans="1:13" ht="44.1" customHeight="1">
       <c r="A33" s="4" t="s">
         <v>317</v>
       </c>
@@ -5785,11 +5557,8 @@
       <c r="M33" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N33" s="5">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="34" spans="1:13" ht="44.1" customHeight="1">
       <c r="A34" s="4" t="s">
         <v>317</v>
       </c>
@@ -5821,11 +5590,8 @@
       <c r="M34" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N34" s="5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="35" spans="1:13" ht="44.1" customHeight="1">
       <c r="A35" s="4" t="s">
         <v>317</v>
       </c>
@@ -5857,11 +5623,8 @@
       <c r="M35" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N35" s="5">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="36" spans="1:13" ht="44.1" customHeight="1">
       <c r="A36" s="4" t="s">
         <v>317</v>
       </c>
@@ -5893,11 +5656,8 @@
       <c r="M36" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N36" s="5">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="37" spans="1:13" ht="44.1" customHeight="1">
       <c r="A37" s="4" t="s">
         <v>317</v>
       </c>
@@ -5929,11 +5689,8 @@
       <c r="M37" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N37" s="5">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="38" spans="1:13" ht="44.1" customHeight="1">
       <c r="A38" s="4" t="s">
         <v>317</v>
       </c>
@@ -5965,11 +5722,8 @@
       <c r="M38" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N38" s="5">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="39" spans="1:13" ht="44.1" customHeight="1">
       <c r="A39" s="4" t="s">
         <v>317</v>
       </c>
@@ -6001,11 +5755,8 @@
       <c r="M39" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N39" s="5">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="40" spans="1:13" ht="44.1" customHeight="1">
       <c r="A40" s="4" t="s">
         <v>317</v>
       </c>
@@ -6037,11 +5788,8 @@
       <c r="M40" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N40" s="5">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="41" spans="1:13" ht="44.1" customHeight="1">
       <c r="A41" s="4" t="s">
         <v>317</v>
       </c>
@@ -6073,11 +5821,8 @@
       <c r="M41" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N41" s="5">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="42" spans="1:13" ht="44.1" customHeight="1">
       <c r="A42" s="4" t="s">
         <v>317</v>
       </c>
@@ -6109,11 +5854,8 @@
       <c r="M42" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N42" s="5">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="43" spans="1:13" ht="44.1" customHeight="1">
       <c r="A43" s="4" t="s">
         <v>317</v>
       </c>
@@ -6145,11 +5887,8 @@
       <c r="M43" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N43" s="5">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="44" spans="1:13" ht="44.1" customHeight="1">
       <c r="A44" s="4" t="s">
         <v>317</v>
       </c>
@@ -6181,11 +5920,8 @@
       <c r="M44" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N44" s="5">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="45" spans="1:13" ht="44.1" customHeight="1">
       <c r="A45" s="4" t="s">
         <v>390</v>
       </c>
@@ -6217,11 +5953,8 @@
       <c r="M45" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N45" s="5">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="46" spans="1:13" ht="44.1" customHeight="1">
       <c r="A46" s="4" t="s">
         <v>390</v>
       </c>
@@ -6253,11 +5986,8 @@
       <c r="M46" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N46" s="5">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="47" spans="1:13" ht="44.1" customHeight="1">
       <c r="A47" s="4" t="s">
         <v>390</v>
       </c>
@@ -6289,11 +6019,8 @@
       <c r="M47" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N47" s="5">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="48" spans="1:13" ht="44.1" customHeight="1">
       <c r="A48" s="4" t="s">
         <v>390</v>
       </c>
@@ -6325,11 +6052,8 @@
       <c r="M48" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N48" s="5">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="49" spans="1:13" ht="44.1" customHeight="1">
       <c r="A49" s="4" t="s">
         <v>390</v>
       </c>
@@ -6361,11 +6085,8 @@
       <c r="M49" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N49" s="5">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="50" spans="1:13" ht="44.1" customHeight="1">
       <c r="A50" s="4" t="s">
         <v>390</v>
       </c>
@@ -6397,11 +6118,8 @@
       <c r="M50" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N50" s="5">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="51" spans="1:13" ht="44.1" customHeight="1">
       <c r="A51" s="4" t="s">
         <v>390</v>
       </c>
@@ -6433,11 +6151,8 @@
       <c r="M51" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N51" s="5">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="52" spans="1:13" ht="44.1" customHeight="1">
       <c r="A52" s="4" t="s">
         <v>390</v>
       </c>
@@ -6469,11 +6184,8 @@
       <c r="M52" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N52" s="5">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="53" spans="1:13" ht="44.1" customHeight="1">
       <c r="A53" s="4" t="s">
         <v>390</v>
       </c>
@@ -6505,11 +6217,8 @@
       <c r="M53" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N53" s="5">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="54" spans="1:13" ht="44.1" customHeight="1">
       <c r="A54" s="4" t="s">
         <v>390</v>
       </c>
@@ -6541,11 +6250,8 @@
       <c r="M54" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N54" s="5">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="55" spans="1:13" ht="44.1" customHeight="1">
       <c r="A55" s="4" t="s">
         <v>390</v>
       </c>
@@ -6577,11 +6283,8 @@
       <c r="M55" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N55" s="5">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="56" spans="1:13" ht="44.1" customHeight="1">
       <c r="A56" s="4" t="s">
         <v>390</v>
       </c>
@@ -6613,11 +6316,8 @@
       <c r="M56" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N56" s="5">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="57" spans="1:13" ht="44.1" customHeight="1">
       <c r="A57" s="4" t="s">
         <v>390</v>
       </c>
@@ -6649,11 +6349,8 @@
       <c r="M57" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N57" s="5">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="58" spans="1:13" ht="44.1" customHeight="1">
       <c r="A58" s="4" t="s">
         <v>390</v>
       </c>
@@ -6685,11 +6382,8 @@
       <c r="M58" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N58" s="5">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="59" spans="1:13" ht="44.1" customHeight="1">
       <c r="A59" s="4" t="s">
         <v>390</v>
       </c>
@@ -6721,11 +6415,8 @@
       <c r="M59" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N59" s="5">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="60" spans="1:13" ht="44.1" customHeight="1">
       <c r="A60" s="4" t="s">
         <v>390</v>
       </c>
@@ -6757,11 +6448,8 @@
       <c r="M60" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N60" s="5">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="61" spans="1:13" ht="44.1" customHeight="1">
       <c r="A61" s="4" t="s">
         <v>390</v>
       </c>
@@ -6793,11 +6481,8 @@
       <c r="M61" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N61" s="5">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="62" spans="1:13" ht="44.1" customHeight="1">
       <c r="A62" s="4" t="s">
         <v>390</v>
       </c>
@@ -6829,11 +6514,8 @@
       <c r="M62" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N62" s="5">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="63" spans="1:13" ht="44.1" customHeight="1">
       <c r="A63" s="4" t="s">
         <v>390</v>
       </c>
@@ -6865,11 +6547,8 @@
       <c r="M63" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N63" s="5">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="64" spans="1:13" ht="44.1" customHeight="1">
       <c r="A64" s="4" t="s">
         <v>390</v>
       </c>
@@ -6901,11 +6580,8 @@
       <c r="M64" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N64" s="5">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="65" spans="1:13" ht="44.1" customHeight="1">
       <c r="A65" s="4" t="s">
         <v>463</v>
       </c>
@@ -6937,11 +6613,8 @@
       <c r="M65" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N65" s="5">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="66" spans="1:13" ht="44.1" customHeight="1">
       <c r="A66" s="4" t="s">
         <v>463</v>
       </c>
@@ -6973,11 +6646,8 @@
       <c r="M66" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N66" s="5">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="67" spans="1:13" ht="44.1" customHeight="1">
       <c r="A67" s="4" t="s">
         <v>463</v>
       </c>
@@ -7009,11 +6679,8 @@
       <c r="M67" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N67" s="5">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="68" spans="1:13" ht="44.1" customHeight="1">
       <c r="A68" s="4" t="s">
         <v>463</v>
       </c>
@@ -7045,11 +6712,8 @@
       <c r="M68" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N68" s="5">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="69" spans="1:13" ht="44.1" customHeight="1">
       <c r="A69" s="4" t="s">
         <v>463</v>
       </c>
@@ -7081,11 +6745,8 @@
       <c r="M69" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N69" s="5">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="70" spans="1:13" ht="44.1" customHeight="1">
       <c r="A70" s="4" t="s">
         <v>463</v>
       </c>
@@ -7117,11 +6778,8 @@
       <c r="M70" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N70" s="5">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="71" spans="1:13" ht="44.1" customHeight="1">
       <c r="A71" s="4" t="s">
         <v>463</v>
       </c>
@@ -7153,11 +6811,8 @@
       <c r="M71" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N71" s="5">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="72" spans="1:13" ht="44.1" customHeight="1">
       <c r="A72" s="4" t="s">
         <v>463</v>
       </c>
@@ -7189,11 +6844,8 @@
       <c r="M72" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N72" s="5">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="73" spans="1:13" ht="44.1" customHeight="1">
       <c r="A73" s="4" t="s">
         <v>463</v>
       </c>
@@ -7225,11 +6877,8 @@
       <c r="M73" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N73" s="5">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="74" spans="1:13" ht="44.1" customHeight="1">
       <c r="A74" s="4" t="s">
         <v>463</v>
       </c>
@@ -7261,11 +6910,8 @@
       <c r="M74" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N74" s="5">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="75" spans="1:13" ht="44.1" customHeight="1">
       <c r="A75" s="4" t="s">
         <v>463</v>
       </c>
@@ -7297,11 +6943,8 @@
       <c r="M75" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N75" s="5">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="76" spans="1:13" ht="44.1" customHeight="1">
       <c r="A76" s="4" t="s">
         <v>463</v>
       </c>
@@ -7333,11 +6976,8 @@
       <c r="M76" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N76" s="5">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="77" spans="1:13" ht="44.1" customHeight="1">
       <c r="A77" s="4" t="s">
         <v>463</v>
       </c>
@@ -7369,11 +7009,8 @@
       <c r="M77" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N77" s="5">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="78" spans="1:13" ht="44.1" customHeight="1">
       <c r="A78" s="4" t="s">
         <v>463</v>
       </c>
@@ -7405,11 +7042,8 @@
       <c r="M78" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N78" s="5">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="79" spans="1:13" ht="44.1" customHeight="1">
       <c r="A79" s="4" t="s">
         <v>463</v>
       </c>
@@ -7441,11 +7075,8 @@
       <c r="M79" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N79" s="5">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="80" spans="1:13" ht="44.1" customHeight="1">
       <c r="A80" s="4" t="s">
         <v>463</v>
       </c>
@@ -7477,11 +7108,8 @@
       <c r="M80" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N80" s="5">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="81" spans="1:13" ht="44.1" customHeight="1">
       <c r="A81" s="4" t="s">
         <v>463</v>
       </c>
@@ -7513,11 +7141,8 @@
       <c r="M81" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N81" s="5">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="82" spans="1:13" ht="44.1" customHeight="1">
       <c r="A82" s="4" t="s">
         <v>463</v>
       </c>
@@ -7549,11 +7174,8 @@
       <c r="M82" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N82" s="5">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="83" spans="1:13" ht="44.1" customHeight="1">
       <c r="A83" s="4" t="s">
         <v>463</v>
       </c>
@@ -7585,11 +7207,8 @@
       <c r="M83" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N83" s="5">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="84" spans="1:13" ht="44.1" customHeight="1">
       <c r="A84" s="4" t="s">
         <v>463</v>
       </c>
@@ -7621,11 +7240,8 @@
       <c r="M84" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N84" s="5">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="85" spans="1:13" ht="44.1" customHeight="1">
       <c r="A85" s="4" t="s">
         <v>536</v>
       </c>
@@ -7657,11 +7273,8 @@
       <c r="M85" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N85" s="5">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="86" spans="1:13" ht="44.1" customHeight="1">
       <c r="A86" s="4" t="s">
         <v>536</v>
       </c>
@@ -7693,11 +7306,8 @@
       <c r="M86" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N86" s="5">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="87" spans="1:13" ht="44.1" customHeight="1">
       <c r="A87" s="4" t="s">
         <v>536</v>
       </c>
@@ -7729,11 +7339,8 @@
       <c r="M87" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N87" s="5">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="88" spans="1:13" ht="44.1" customHeight="1">
       <c r="A88" s="4" t="s">
         <v>536</v>
       </c>
@@ -7765,11 +7372,8 @@
       <c r="M88" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N88" s="5">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="89" spans="1:13" ht="44.1" customHeight="1">
       <c r="A89" s="4" t="s">
         <v>536</v>
       </c>
@@ -7801,11 +7405,8 @@
       <c r="M89" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N89" s="5">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="90" spans="1:13" ht="44.1" customHeight="1">
       <c r="A90" s="4" t="s">
         <v>536</v>
       </c>
@@ -7837,11 +7438,8 @@
       <c r="M90" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N90" s="5">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="91" spans="1:13" ht="44.1" customHeight="1">
       <c r="A91" s="4" t="s">
         <v>536</v>
       </c>
@@ -7873,11 +7471,8 @@
       <c r="M91" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N91" s="5">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="92" spans="1:13" ht="44.1" customHeight="1">
       <c r="A92" s="4" t="s">
         <v>536</v>
       </c>
@@ -7909,11 +7504,8 @@
       <c r="M92" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N92" s="5">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="93" spans="1:13" ht="44.1" customHeight="1">
       <c r="A93" s="4" t="s">
         <v>536</v>
       </c>
@@ -7945,11 +7537,8 @@
       <c r="M93" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N93" s="5">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="94" spans="1:13" ht="44.1" customHeight="1">
       <c r="A94" s="4" t="s">
         <v>536</v>
       </c>
@@ -7981,11 +7570,8 @@
       <c r="M94" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N94" s="5">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="95" spans="1:13" ht="44.1" customHeight="1">
       <c r="A95" s="4" t="s">
         <v>536</v>
       </c>
@@ -8017,11 +7603,8 @@
       <c r="M95" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N95" s="5">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="96" spans="1:13" ht="44.1" customHeight="1">
       <c r="A96" s="4" t="s">
         <v>536</v>
       </c>
@@ -8053,11 +7636,8 @@
       <c r="M96" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N96" s="5">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="97" spans="1:13" ht="44.1" customHeight="1">
       <c r="A97" s="4" t="s">
         <v>536</v>
       </c>
@@ -8089,11 +7669,8 @@
       <c r="M97" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N97" s="5">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="98" spans="1:13" ht="44.1" customHeight="1">
       <c r="A98" s="4" t="s">
         <v>536</v>
       </c>
@@ -8125,11 +7702,8 @@
       <c r="M98" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N98" s="5">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="99" spans="1:13" ht="44.1" customHeight="1">
       <c r="A99" s="4" t="s">
         <v>536</v>
       </c>
@@ -8161,11 +7735,8 @@
       <c r="M99" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N99" s="5">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="100" spans="1:13" ht="44.1" customHeight="1">
       <c r="A100" s="4" t="s">
         <v>536</v>
       </c>
@@ -8197,11 +7768,8 @@
       <c r="M100" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N100" s="5">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="101" spans="1:13" ht="44.1" customHeight="1">
       <c r="A101" s="4" t="s">
         <v>536</v>
       </c>
@@ -8233,11 +7801,8 @@
       <c r="M101" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N101" s="5">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="102" spans="1:13" ht="44.1" customHeight="1">
       <c r="A102" s="4" t="s">
         <v>536</v>
       </c>
@@ -8269,11 +7834,8 @@
       <c r="M102" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N102" s="5">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="103" spans="1:13" ht="44.1" customHeight="1">
       <c r="A103" s="4" t="s">
         <v>536</v>
       </c>
@@ -8305,11 +7867,8 @@
       <c r="M103" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N103" s="5">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14" ht="44.1" customHeight="1">
+    </row>
+    <row r="104" spans="1:13" ht="44.1" customHeight="1">
       <c r="A104" s="4" t="s">
         <v>536</v>
       </c>
@@ -8340,9 +7899,6 @@
       </c>
       <c r="M104" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="N104" s="5">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -8367,7 +7923,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>

--- a/public/templates/Maitsys-Assure-Master-Requirement-Import-Template.xlsx
+++ b/public/templates/Maitsys-Assure-Master-Requirement-Import-Template.xlsx
@@ -56,34 +56,6 @@
             <scheme val="minor"/>
           </rPr>
           <t>Stable identifier for this question within its requirement, e.g. LE-01-Q1. Leave blank to auto-generate. Each question row needs its own unique Question ID.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Comma-separated site codes this requirement applies to (e.g. KC-NSM-042, KC-RBM-018). Leave blank to apply to ALL sites — this is the default for most Operating System requirements.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Internal only — never shown to site users. Used for future Top-3-Gap prioritization (Phase 2). Safe to leave blank for Phase 1 import.</t>
         </r>
       </text>
     </comment>
@@ -2632,84 +2604,6 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="42" customHeight="1">
-      <c r="A12" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="42" customHeight="1">
-      <c r="A13" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="11"/>
-    </row>
-    <row r="14" spans="1:4" ht="42" customHeight="1">
-      <c r="A14" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="11"/>
-    </row>
-    <row r="15" spans="1:4" ht="42" customHeight="1">
-      <c r="A15" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="11"/>
-    </row>
-    <row r="16" spans="1:4" ht="42" customHeight="1">
-      <c r="A16" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="42" customHeight="1">
-      <c r="A17" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
     <row r="21" spans="1:4">
       <c r="A21" s="14" t="s">
         <v>46</v>
@@ -2784,7 +2678,7 @@
 
 <file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -2793,24 +2687,19 @@
     <col min="4" max="4" width="40" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="7" width="42" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="30" customHeight="1">
+    <row r="4" spans="1:7" ht="30" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>52</v>
       </c>
@@ -2832,26 +2721,8 @@
       <c r="G4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="5" spans="1:7" ht="45.95" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
@@ -2873,18 +2744,8 @@
       <c r="G5" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="6" spans="1:7" ht="45.95" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
@@ -2906,18 +2767,8 @@
       <c r="G6" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="7" spans="1:7" ht="45.95" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -2939,18 +2790,8 @@
       <c r="G7" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="8" spans="1:7" ht="45.95" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>9</v>
       </c>
@@ -2972,18 +2813,8 @@
       <c r="G8" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="9" spans="1:7" ht="45.95" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>9</v>
       </c>
@@ -3005,18 +2836,8 @@
       <c r="G9" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="10" spans="1:7" ht="45.95" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
@@ -3038,18 +2859,8 @@
       <c r="G10" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="11" spans="1:7" ht="45.95" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
@@ -3071,18 +2882,8 @@
       <c r="G11" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="12" spans="1:7" ht="45.95" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>9</v>
       </c>
@@ -3104,18 +2905,8 @@
       <c r="G12" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="13" spans="1:7" ht="45.95" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>9</v>
       </c>
@@ -3137,18 +2928,8 @@
       <c r="G13" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="14" spans="1:7" ht="45.95" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>9</v>
       </c>
@@ -3170,18 +2951,8 @@
       <c r="G14" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M14" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="15" spans="1:7" ht="45.95" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>9</v>
       </c>
@@ -3203,18 +2974,8 @@
       <c r="G15" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M15" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="16" spans="1:7" ht="45.95" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>9</v>
       </c>
@@ -3236,18 +2997,8 @@
       <c r="G16" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="17" spans="1:7" ht="45.95" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>9</v>
       </c>
@@ -3269,18 +3020,8 @@
       <c r="G17" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M17" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="18" spans="1:7" ht="45.95" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>9</v>
       </c>
@@ -3302,18 +3043,8 @@
       <c r="G18" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="19" spans="1:7" ht="45.95" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>9</v>
       </c>
@@ -3335,18 +3066,8 @@
       <c r="G19" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M19" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="20" spans="1:7" ht="45.95" customHeight="1">
       <c r="A20" s="4" t="s">
         <v>9</v>
       </c>
@@ -3368,18 +3089,8 @@
       <c r="G20" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M20" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="21" spans="1:7" ht="45.95" customHeight="1">
       <c r="A21" s="4" t="s">
         <v>9</v>
       </c>
@@ -3401,18 +3112,8 @@
       <c r="G21" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M21" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="22" spans="1:7" ht="45.95" customHeight="1">
       <c r="A22" s="4" t="s">
         <v>9</v>
       </c>
@@ -3434,18 +3135,8 @@
       <c r="G22" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M22" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="23" spans="1:7" ht="45.95" customHeight="1">
       <c r="A23" s="4" t="s">
         <v>9</v>
       </c>
@@ -3467,18 +3158,8 @@
       <c r="G23" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="24" spans="1:7" ht="45.95" customHeight="1">
       <c r="A24" s="4" t="s">
         <v>9</v>
       </c>
@@ -3500,18 +3181,8 @@
       <c r="G24" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M24" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="25" spans="1:7" ht="45.95" customHeight="1">
       <c r="A25" s="4" t="s">
         <v>9</v>
       </c>
@@ -3533,18 +3204,8 @@
       <c r="G25" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M25" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="26" spans="1:7" ht="45.95" customHeight="1">
       <c r="A26" s="4" t="s">
         <v>9</v>
       </c>
@@ -3566,18 +3227,8 @@
       <c r="G26" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M26" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="27" spans="1:7" ht="45.95" customHeight="1">
       <c r="A27" s="4" t="s">
         <v>9</v>
       </c>
@@ -3599,18 +3250,8 @@
       <c r="G27" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M27" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="28" spans="1:7" ht="45.95" customHeight="1">
       <c r="A28" s="4" t="s">
         <v>9</v>
       </c>
@@ -3632,18 +3273,8 @@
       <c r="G28" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M28" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="29" spans="1:7" ht="45.95" customHeight="1">
       <c r="A29" s="4" t="s">
         <v>9</v>
       </c>
@@ -3665,18 +3296,8 @@
       <c r="G29" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M29" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="30" spans="1:7" ht="45.95" customHeight="1">
       <c r="A30" s="4" t="s">
         <v>9</v>
       </c>
@@ -3698,18 +3319,8 @@
       <c r="G30" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M30" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="31" spans="1:7" ht="45.95" customHeight="1">
       <c r="A31" s="4" t="s">
         <v>9</v>
       </c>
@@ -3731,18 +3342,8 @@
       <c r="G31" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M31" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="32" spans="1:7" ht="45.95" customHeight="1">
       <c r="A32" s="4" t="s">
         <v>9</v>
       </c>
@@ -3764,18 +3365,8 @@
       <c r="G32" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M32" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="33" spans="1:7" ht="45.95" customHeight="1">
       <c r="A33" s="4" t="s">
         <v>9</v>
       </c>
@@ -3797,18 +3388,8 @@
       <c r="G33" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M33" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="34" spans="1:7" ht="45.95" customHeight="1">
       <c r="A34" s="4" t="s">
         <v>9</v>
       </c>
@@ -3830,18 +3411,8 @@
       <c r="G34" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
-      <c r="L34" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M34" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="35" spans="1:7" ht="45.95" customHeight="1">
       <c r="A35" s="4" t="s">
         <v>9</v>
       </c>
@@ -3863,18 +3434,8 @@
       <c r="G35" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
-      <c r="L35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M35" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="36" spans="1:7" ht="45.95" customHeight="1">
       <c r="A36" s="4" t="s">
         <v>9</v>
       </c>
@@ -3896,18 +3457,8 @@
       <c r="G36" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M36" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="37" spans="1:7" ht="45.95" customHeight="1">
       <c r="A37" s="4" t="s">
         <v>9</v>
       </c>
@@ -3929,18 +3480,8 @@
       <c r="G37" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M37" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="38" spans="1:7" ht="45.95" customHeight="1">
       <c r="A38" s="4" t="s">
         <v>9</v>
       </c>
@@ -3962,18 +3503,8 @@
       <c r="G38" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M38" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="39" spans="1:7" ht="45.95" customHeight="1">
       <c r="A39" s="4" t="s">
         <v>9</v>
       </c>
@@ -3995,18 +3526,8 @@
       <c r="G39" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M39" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="40" spans="1:7" ht="45.95" customHeight="1">
       <c r="A40" s="4" t="s">
         <v>9</v>
       </c>
@@ -4028,18 +3549,8 @@
       <c r="G40" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M40" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="41" spans="1:7" ht="45.95" customHeight="1">
       <c r="A41" s="4" t="s">
         <v>9</v>
       </c>
@@ -4061,18 +3572,8 @@
       <c r="G41" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5"/>
-      <c r="L41" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M41" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="42" spans="1:7" ht="45.95" customHeight="1">
       <c r="A42" s="4" t="s">
         <v>9</v>
       </c>
@@ -4094,18 +3595,8 @@
       <c r="G42" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="5"/>
-      <c r="K42" s="5"/>
-      <c r="L42" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M42" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="43" spans="1:7" ht="45.95" customHeight="1">
       <c r="A43" s="4" t="s">
         <v>9</v>
       </c>
@@ -4127,18 +3618,8 @@
       <c r="G43" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M43" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="44" spans="1:7" ht="45.95" customHeight="1">
       <c r="A44" s="4" t="s">
         <v>9</v>
       </c>
@@ -4160,18 +3641,8 @@
       <c r="G44" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="5"/>
-      <c r="K44" s="5"/>
-      <c r="L44" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M44" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="45" spans="1:7" ht="45.95" customHeight="1">
       <c r="A45" s="4" t="s">
         <v>9</v>
       </c>
@@ -4193,18 +3664,8 @@
       <c r="G45" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="5"/>
-      <c r="K45" s="5"/>
-      <c r="L45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M45" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="46" spans="1:7" ht="45.95" customHeight="1">
       <c r="A46" s="4" t="s">
         <v>9</v>
       </c>
@@ -4226,18 +3687,8 @@
       <c r="G46" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="5"/>
-      <c r="K46" s="5"/>
-      <c r="L46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M46" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="47" spans="1:7" ht="45.95" customHeight="1">
       <c r="A47" s="4" t="s">
         <v>9</v>
       </c>
@@ -4259,18 +3710,8 @@
       <c r="G47" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5"/>
-      <c r="J47" s="5"/>
-      <c r="K47" s="5"/>
-      <c r="L47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M47" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="48" spans="1:7" ht="45.95" customHeight="1">
       <c r="A48" s="4" t="s">
         <v>9</v>
       </c>
@@ -4292,18 +3733,8 @@
       <c r="G48" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="H48" s="5"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="5"/>
-      <c r="K48" s="5"/>
-      <c r="L48" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M48" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="49" spans="1:7" ht="45.95" customHeight="1">
       <c r="A49" s="4" t="s">
         <v>9</v>
       </c>
@@ -4325,18 +3756,8 @@
       <c r="G49" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="H49" s="5"/>
-      <c r="I49" s="5"/>
-      <c r="J49" s="5"/>
-      <c r="K49" s="5"/>
-      <c r="L49" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M49" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="45.95" customHeight="1">
+    </row>
+    <row r="50" spans="1:7" ht="45.95" customHeight="1">
       <c r="A50" s="4" t="s">
         <v>9</v>
       </c>
@@ -4358,18 +3779,8 @@
       <c r="G50" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="H50" s="5"/>
-      <c r="I50" s="5"/>
-      <c r="J50" s="5"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M50" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13">
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" s="6" t="s">
         <v>234</v>
       </c>
@@ -4391,20 +3802,8 @@
       <c r="G51" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="H51" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
-      <c r="L51" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="M51" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13">
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="9"/>
@@ -4412,14 +3811,8 @@
       <c r="E52" s="9"/>
       <c r="F52" s="8"/>
       <c r="G52" s="8"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="9"/>
-      <c r="J52" s="9"/>
-      <c r="K52" s="9"/>
-      <c r="L52" s="9"/>
-      <c r="M52" s="9"/>
-    </row>
-    <row r="53" spans="1:13">
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="9"/>
@@ -4427,14 +3820,8 @@
       <c r="E53" s="9"/>
       <c r="F53" s="8"/>
       <c r="G53" s="8"/>
-      <c r="H53" s="9"/>
-      <c r="I53" s="9"/>
-      <c r="J53" s="9"/>
-      <c r="K53" s="9"/>
-      <c r="L53" s="9"/>
-      <c r="M53" s="9"/>
-    </row>
-    <row r="54" spans="1:13">
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="9"/>
@@ -4442,14 +3829,8 @@
       <c r="E54" s="9"/>
       <c r="F54" s="8"/>
       <c r="G54" s="8"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="9"/>
-      <c r="J54" s="9"/>
-      <c r="K54" s="9"/>
-      <c r="L54" s="9"/>
-      <c r="M54" s="9"/>
-    </row>
-    <row r="55" spans="1:13">
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="9"/>
@@ -4457,14 +3838,8 @@
       <c r="E55" s="9"/>
       <c r="F55" s="8"/>
       <c r="G55" s="8"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="9"/>
-      <c r="J55" s="9"/>
-      <c r="K55" s="9"/>
-      <c r="L55" s="9"/>
-      <c r="M55" s="9"/>
-    </row>
-    <row r="56" spans="1:13">
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="9"/>
@@ -4472,14 +3847,8 @@
       <c r="E56" s="9"/>
       <c r="F56" s="8"/>
       <c r="G56" s="8"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="9"/>
-      <c r="J56" s="9"/>
-      <c r="K56" s="9"/>
-      <c r="L56" s="9"/>
-      <c r="M56" s="9"/>
-    </row>
-    <row r="57" spans="1:13">
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="9"/>
@@ -4487,14 +3856,8 @@
       <c r="E57" s="9"/>
       <c r="F57" s="8"/>
       <c r="G57" s="8"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="9"/>
-      <c r="J57" s="9"/>
-      <c r="K57" s="9"/>
-      <c r="L57" s="9"/>
-      <c r="M57" s="9"/>
-    </row>
-    <row r="58" spans="1:13">
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" s="8"/>
       <c r="B58" s="8"/>
       <c r="C58" s="9"/>
@@ -4502,19 +3865,8 @@
       <c r="E58" s="9"/>
       <c r="F58" s="8"/>
       <c r="G58" s="8"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="9"/>
-      <c r="J58" s="9"/>
-      <c r="K58" s="9"/>
-      <c r="L58" s="9"/>
-      <c r="M58" s="9"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="M5:M58" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"Draft,Published"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
   <extLst>
@@ -4534,7 +3886,7 @@
 
 <file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:M104"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -4543,24 +3895,19 @@
     <col min="4" max="4" width="40" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="7" width="42" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="30" customHeight="1">
+    <row r="4" spans="1:7" ht="30" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>52</v>
       </c>
@@ -4582,26 +3929,8 @@
       <c r="G4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="5" spans="1:7" ht="44.1" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>244</v>
       </c>
@@ -4623,18 +3952,8 @@
       <c r="G5" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="6" spans="1:7" ht="44.1" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>244</v>
       </c>
@@ -4656,18 +3975,8 @@
       <c r="G6" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="7" spans="1:7" ht="44.1" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>244</v>
       </c>
@@ -4689,18 +3998,8 @@
       <c r="G7" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="8" spans="1:7" ht="44.1" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>244</v>
       </c>
@@ -4722,18 +4021,8 @@
       <c r="G8" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="9" spans="1:7" ht="44.1" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>244</v>
       </c>
@@ -4755,18 +4044,8 @@
       <c r="G9" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="10" spans="1:7" ht="44.1" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>244</v>
       </c>
@@ -4788,18 +4067,8 @@
       <c r="G10" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="11" spans="1:7" ht="44.1" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>244</v>
       </c>
@@ -4821,18 +4090,8 @@
       <c r="G11" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="12" spans="1:7" ht="44.1" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>244</v>
       </c>
@@ -4854,18 +4113,8 @@
       <c r="G12" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="13" spans="1:7" ht="44.1" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>244</v>
       </c>
@@ -4887,18 +4136,8 @@
       <c r="G13" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="14" spans="1:7" ht="44.1" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>244</v>
       </c>
@@ -4920,18 +4159,8 @@
       <c r="G14" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M14" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="15" spans="1:7" ht="44.1" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>244</v>
       </c>
@@ -4953,18 +4182,8 @@
       <c r="G15" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M15" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="16" spans="1:7" ht="44.1" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>244</v>
       </c>
@@ -4986,18 +4205,8 @@
       <c r="G16" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="17" spans="1:7" ht="44.1" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>244</v>
       </c>
@@ -5019,18 +4228,8 @@
       <c r="G17" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M17" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="18" spans="1:7" ht="44.1" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>244</v>
       </c>
@@ -5052,18 +4251,8 @@
       <c r="G18" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="19" spans="1:7" ht="44.1" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>244</v>
       </c>
@@ -5085,18 +4274,8 @@
       <c r="G19" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M19" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="20" spans="1:7" ht="44.1" customHeight="1">
       <c r="A20" s="4" t="s">
         <v>244</v>
       </c>
@@ -5118,18 +4297,8 @@
       <c r="G20" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M20" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="21" spans="1:7" ht="44.1" customHeight="1">
       <c r="A21" s="4" t="s">
         <v>244</v>
       </c>
@@ -5151,18 +4320,8 @@
       <c r="G21" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M21" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="22" spans="1:7" ht="44.1" customHeight="1">
       <c r="A22" s="4" t="s">
         <v>244</v>
       </c>
@@ -5184,18 +4343,8 @@
       <c r="G22" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M22" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="23" spans="1:7" ht="44.1" customHeight="1">
       <c r="A23" s="4" t="s">
         <v>244</v>
       </c>
@@ -5217,18 +4366,8 @@
       <c r="G23" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="24" spans="1:7" ht="44.1" customHeight="1">
       <c r="A24" s="4" t="s">
         <v>244</v>
       </c>
@@ -5250,18 +4389,8 @@
       <c r="G24" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M24" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="25" spans="1:7" ht="44.1" customHeight="1">
       <c r="A25" s="4" t="s">
         <v>317</v>
       </c>
@@ -5283,18 +4412,8 @@
       <c r="G25" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M25" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="26" spans="1:7" ht="44.1" customHeight="1">
       <c r="A26" s="4" t="s">
         <v>317</v>
       </c>
@@ -5316,18 +4435,8 @@
       <c r="G26" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M26" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="27" spans="1:7" ht="44.1" customHeight="1">
       <c r="A27" s="4" t="s">
         <v>317</v>
       </c>
@@ -5349,18 +4458,8 @@
       <c r="G27" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M27" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="28" spans="1:7" ht="44.1" customHeight="1">
       <c r="A28" s="4" t="s">
         <v>317</v>
       </c>
@@ -5382,18 +4481,8 @@
       <c r="G28" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M28" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="29" spans="1:7" ht="44.1" customHeight="1">
       <c r="A29" s="4" t="s">
         <v>317</v>
       </c>
@@ -5415,18 +4504,8 @@
       <c r="G29" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M29" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="30" spans="1:7" ht="44.1" customHeight="1">
       <c r="A30" s="4" t="s">
         <v>317</v>
       </c>
@@ -5448,18 +4527,8 @@
       <c r="G30" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M30" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="31" spans="1:7" ht="44.1" customHeight="1">
       <c r="A31" s="4" t="s">
         <v>317</v>
       </c>
@@ -5481,18 +4550,8 @@
       <c r="G31" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M31" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="32" spans="1:7" ht="44.1" customHeight="1">
       <c r="A32" s="4" t="s">
         <v>317</v>
       </c>
@@ -5514,18 +4573,8 @@
       <c r="G32" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M32" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="33" spans="1:7" ht="44.1" customHeight="1">
       <c r="A33" s="4" t="s">
         <v>317</v>
       </c>
@@ -5547,18 +4596,8 @@
       <c r="G33" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M33" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="34" spans="1:7" ht="44.1" customHeight="1">
       <c r="A34" s="4" t="s">
         <v>317</v>
       </c>
@@ -5580,18 +4619,8 @@
       <c r="G34" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
-      <c r="L34" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M34" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="35" spans="1:7" ht="44.1" customHeight="1">
       <c r="A35" s="4" t="s">
         <v>317</v>
       </c>
@@ -5613,18 +4642,8 @@
       <c r="G35" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
-      <c r="L35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M35" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="36" spans="1:7" ht="44.1" customHeight="1">
       <c r="A36" s="4" t="s">
         <v>317</v>
       </c>
@@ -5646,18 +4665,8 @@
       <c r="G36" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M36" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="37" spans="1:7" ht="44.1" customHeight="1">
       <c r="A37" s="4" t="s">
         <v>317</v>
       </c>
@@ -5679,18 +4688,8 @@
       <c r="G37" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M37" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="38" spans="1:7" ht="44.1" customHeight="1">
       <c r="A38" s="4" t="s">
         <v>317</v>
       </c>
@@ -5712,18 +4711,8 @@
       <c r="G38" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M38" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="39" spans="1:7" ht="44.1" customHeight="1">
       <c r="A39" s="4" t="s">
         <v>317</v>
       </c>
@@ -5745,18 +4734,8 @@
       <c r="G39" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M39" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="40" spans="1:7" ht="44.1" customHeight="1">
       <c r="A40" s="4" t="s">
         <v>317</v>
       </c>
@@ -5778,18 +4757,8 @@
       <c r="G40" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M40" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="41" spans="1:7" ht="44.1" customHeight="1">
       <c r="A41" s="4" t="s">
         <v>317</v>
       </c>
@@ -5811,18 +4780,8 @@
       <c r="G41" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5"/>
-      <c r="L41" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M41" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="42" spans="1:7" ht="44.1" customHeight="1">
       <c r="A42" s="4" t="s">
         <v>317</v>
       </c>
@@ -5844,18 +4803,8 @@
       <c r="G42" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="5"/>
-      <c r="K42" s="5"/>
-      <c r="L42" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M42" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="43" spans="1:7" ht="44.1" customHeight="1">
       <c r="A43" s="4" t="s">
         <v>317</v>
       </c>
@@ -5877,18 +4826,8 @@
       <c r="G43" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M43" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="44" spans="1:7" ht="44.1" customHeight="1">
       <c r="A44" s="4" t="s">
         <v>317</v>
       </c>
@@ -5910,18 +4849,8 @@
       <c r="G44" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="5"/>
-      <c r="K44" s="5"/>
-      <c r="L44" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M44" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="45" spans="1:7" ht="44.1" customHeight="1">
       <c r="A45" s="4" t="s">
         <v>390</v>
       </c>
@@ -5943,18 +4872,8 @@
       <c r="G45" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="5"/>
-      <c r="K45" s="5"/>
-      <c r="L45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M45" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="46" spans="1:7" ht="44.1" customHeight="1">
       <c r="A46" s="4" t="s">
         <v>390</v>
       </c>
@@ -5976,18 +4895,8 @@
       <c r="G46" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="5"/>
-      <c r="K46" s="5"/>
-      <c r="L46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M46" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="47" spans="1:7" ht="44.1" customHeight="1">
       <c r="A47" s="4" t="s">
         <v>390</v>
       </c>
@@ -6009,18 +4918,8 @@
       <c r="G47" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5"/>
-      <c r="J47" s="5"/>
-      <c r="K47" s="5"/>
-      <c r="L47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M47" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="48" spans="1:7" ht="44.1" customHeight="1">
       <c r="A48" s="4" t="s">
         <v>390</v>
       </c>
@@ -6042,18 +4941,8 @@
       <c r="G48" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="H48" s="5"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="5"/>
-      <c r="K48" s="5"/>
-      <c r="L48" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M48" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="49" spans="1:7" ht="44.1" customHeight="1">
       <c r="A49" s="4" t="s">
         <v>390</v>
       </c>
@@ -6075,18 +4964,8 @@
       <c r="G49" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="H49" s="5"/>
-      <c r="I49" s="5"/>
-      <c r="J49" s="5"/>
-      <c r="K49" s="5"/>
-      <c r="L49" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M49" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="50" spans="1:7" ht="44.1" customHeight="1">
       <c r="A50" s="4" t="s">
         <v>390</v>
       </c>
@@ -6108,18 +4987,8 @@
       <c r="G50" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="H50" s="5"/>
-      <c r="I50" s="5"/>
-      <c r="J50" s="5"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M50" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="51" spans="1:7" ht="44.1" customHeight="1">
       <c r="A51" s="4" t="s">
         <v>390</v>
       </c>
@@ -6141,18 +5010,8 @@
       <c r="G51" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
-      <c r="J51" s="5"/>
-      <c r="K51" s="5"/>
-      <c r="L51" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M51" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="52" spans="1:7" ht="44.1" customHeight="1">
       <c r="A52" s="4" t="s">
         <v>390</v>
       </c>
@@ -6174,18 +5033,8 @@
       <c r="G52" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="H52" s="5"/>
-      <c r="I52" s="5"/>
-      <c r="J52" s="5"/>
-      <c r="K52" s="5"/>
-      <c r="L52" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M52" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="53" spans="1:7" ht="44.1" customHeight="1">
       <c r="A53" s="4" t="s">
         <v>390</v>
       </c>
@@ -6207,18 +5056,8 @@
       <c r="G53" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="H53" s="5"/>
-      <c r="I53" s="5"/>
-      <c r="J53" s="5"/>
-      <c r="K53" s="5"/>
-      <c r="L53" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M53" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="54" spans="1:7" ht="44.1" customHeight="1">
       <c r="A54" s="4" t="s">
         <v>390</v>
       </c>
@@ -6240,18 +5079,8 @@
       <c r="G54" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="H54" s="5"/>
-      <c r="I54" s="5"/>
-      <c r="J54" s="5"/>
-      <c r="K54" s="5"/>
-      <c r="L54" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M54" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="55" spans="1:7" ht="44.1" customHeight="1">
       <c r="A55" s="4" t="s">
         <v>390</v>
       </c>
@@ -6273,18 +5102,8 @@
       <c r="G55" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="H55" s="5"/>
-      <c r="I55" s="5"/>
-      <c r="J55" s="5"/>
-      <c r="K55" s="5"/>
-      <c r="L55" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M55" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="56" spans="1:7" ht="44.1" customHeight="1">
       <c r="A56" s="4" t="s">
         <v>390</v>
       </c>
@@ -6306,18 +5125,8 @@
       <c r="G56" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="H56" s="5"/>
-      <c r="I56" s="5"/>
-      <c r="J56" s="5"/>
-      <c r="K56" s="5"/>
-      <c r="L56" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M56" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="57" spans="1:7" ht="44.1" customHeight="1">
       <c r="A57" s="4" t="s">
         <v>390</v>
       </c>
@@ -6339,18 +5148,8 @@
       <c r="G57" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="H57" s="5"/>
-      <c r="I57" s="5"/>
-      <c r="J57" s="5"/>
-      <c r="K57" s="5"/>
-      <c r="L57" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M57" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="58" spans="1:7" ht="44.1" customHeight="1">
       <c r="A58" s="4" t="s">
         <v>390</v>
       </c>
@@ -6372,18 +5171,8 @@
       <c r="G58" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="H58" s="5"/>
-      <c r="I58" s="5"/>
-      <c r="J58" s="5"/>
-      <c r="K58" s="5"/>
-      <c r="L58" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M58" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="59" spans="1:7" ht="44.1" customHeight="1">
       <c r="A59" s="4" t="s">
         <v>390</v>
       </c>
@@ -6405,18 +5194,8 @@
       <c r="G59" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="H59" s="5"/>
-      <c r="I59" s="5"/>
-      <c r="J59" s="5"/>
-      <c r="K59" s="5"/>
-      <c r="L59" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M59" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="60" spans="1:7" ht="44.1" customHeight="1">
       <c r="A60" s="4" t="s">
         <v>390</v>
       </c>
@@ -6438,18 +5217,8 @@
       <c r="G60" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="H60" s="5"/>
-      <c r="I60" s="5"/>
-      <c r="J60" s="5"/>
-      <c r="K60" s="5"/>
-      <c r="L60" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M60" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="61" spans="1:7" ht="44.1" customHeight="1">
       <c r="A61" s="4" t="s">
         <v>390</v>
       </c>
@@ -6471,18 +5240,8 @@
       <c r="G61" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="H61" s="5"/>
-      <c r="I61" s="5"/>
-      <c r="J61" s="5"/>
-      <c r="K61" s="5"/>
-      <c r="L61" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M61" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="62" spans="1:7" ht="44.1" customHeight="1">
       <c r="A62" s="4" t="s">
         <v>390</v>
       </c>
@@ -6504,18 +5263,8 @@
       <c r="G62" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="H62" s="5"/>
-      <c r="I62" s="5"/>
-      <c r="J62" s="5"/>
-      <c r="K62" s="5"/>
-      <c r="L62" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M62" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="63" spans="1:7" ht="44.1" customHeight="1">
       <c r="A63" s="4" t="s">
         <v>390</v>
       </c>
@@ -6537,18 +5286,8 @@
       <c r="G63" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="H63" s="5"/>
-      <c r="I63" s="5"/>
-      <c r="J63" s="5"/>
-      <c r="K63" s="5"/>
-      <c r="L63" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M63" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="64" spans="1:7" ht="44.1" customHeight="1">
       <c r="A64" s="4" t="s">
         <v>390</v>
       </c>
@@ -6570,18 +5309,8 @@
       <c r="G64" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="H64" s="5"/>
-      <c r="I64" s="5"/>
-      <c r="J64" s="5"/>
-      <c r="K64" s="5"/>
-      <c r="L64" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M64" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="65" spans="1:7" ht="44.1" customHeight="1">
       <c r="A65" s="4" t="s">
         <v>463</v>
       </c>
@@ -6603,18 +5332,8 @@
       <c r="G65" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="H65" s="5"/>
-      <c r="I65" s="5"/>
-      <c r="J65" s="5"/>
-      <c r="K65" s="5"/>
-      <c r="L65" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M65" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="66" spans="1:7" ht="44.1" customHeight="1">
       <c r="A66" s="4" t="s">
         <v>463</v>
       </c>
@@ -6636,18 +5355,8 @@
       <c r="G66" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="H66" s="5"/>
-      <c r="I66" s="5"/>
-      <c r="J66" s="5"/>
-      <c r="K66" s="5"/>
-      <c r="L66" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M66" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="67" spans="1:7" ht="44.1" customHeight="1">
       <c r="A67" s="4" t="s">
         <v>463</v>
       </c>
@@ -6669,18 +5378,8 @@
       <c r="G67" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="H67" s="5"/>
-      <c r="I67" s="5"/>
-      <c r="J67" s="5"/>
-      <c r="K67" s="5"/>
-      <c r="L67" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M67" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="68" spans="1:7" ht="44.1" customHeight="1">
       <c r="A68" s="4" t="s">
         <v>463</v>
       </c>
@@ -6702,18 +5401,8 @@
       <c r="G68" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="H68" s="5"/>
-      <c r="I68" s="5"/>
-      <c r="J68" s="5"/>
-      <c r="K68" s="5"/>
-      <c r="L68" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M68" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="69" spans="1:7" ht="44.1" customHeight="1">
       <c r="A69" s="4" t="s">
         <v>463</v>
       </c>
@@ -6735,18 +5424,8 @@
       <c r="G69" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="H69" s="5"/>
-      <c r="I69" s="5"/>
-      <c r="J69" s="5"/>
-      <c r="K69" s="5"/>
-      <c r="L69" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M69" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="70" spans="1:7" ht="44.1" customHeight="1">
       <c r="A70" s="4" t="s">
         <v>463</v>
       </c>
@@ -6768,18 +5447,8 @@
       <c r="G70" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="H70" s="5"/>
-      <c r="I70" s="5"/>
-      <c r="J70" s="5"/>
-      <c r="K70" s="5"/>
-      <c r="L70" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M70" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="71" spans="1:7" ht="44.1" customHeight="1">
       <c r="A71" s="4" t="s">
         <v>463</v>
       </c>
@@ -6801,18 +5470,8 @@
       <c r="G71" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="H71" s="5"/>
-      <c r="I71" s="5"/>
-      <c r="J71" s="5"/>
-      <c r="K71" s="5"/>
-      <c r="L71" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M71" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="72" spans="1:7" ht="44.1" customHeight="1">
       <c r="A72" s="4" t="s">
         <v>463</v>
       </c>
@@ -6834,18 +5493,8 @@
       <c r="G72" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="H72" s="5"/>
-      <c r="I72" s="5"/>
-      <c r="J72" s="5"/>
-      <c r="K72" s="5"/>
-      <c r="L72" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M72" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="73" spans="1:7" ht="44.1" customHeight="1">
       <c r="A73" s="4" t="s">
         <v>463</v>
       </c>
@@ -6867,18 +5516,8 @@
       <c r="G73" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="H73" s="5"/>
-      <c r="I73" s="5"/>
-      <c r="J73" s="5"/>
-      <c r="K73" s="5"/>
-      <c r="L73" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M73" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="74" spans="1:7" ht="44.1" customHeight="1">
       <c r="A74" s="4" t="s">
         <v>463</v>
       </c>
@@ -6900,18 +5539,8 @@
       <c r="G74" s="4" t="s">
         <v>499</v>
       </c>
-      <c r="H74" s="5"/>
-      <c r="I74" s="5"/>
-      <c r="J74" s="5"/>
-      <c r="K74" s="5"/>
-      <c r="L74" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M74" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="75" spans="1:7" ht="44.1" customHeight="1">
       <c r="A75" s="4" t="s">
         <v>463</v>
       </c>
@@ -6933,18 +5562,8 @@
       <c r="G75" s="4" t="s">
         <v>505</v>
       </c>
-      <c r="H75" s="5"/>
-      <c r="I75" s="5"/>
-      <c r="J75" s="5"/>
-      <c r="K75" s="5"/>
-      <c r="L75" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M75" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="76" spans="1:7" ht="44.1" customHeight="1">
       <c r="A76" s="4" t="s">
         <v>463</v>
       </c>
@@ -6966,18 +5585,8 @@
       <c r="G76" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="H76" s="5"/>
-      <c r="I76" s="5"/>
-      <c r="J76" s="5"/>
-      <c r="K76" s="5"/>
-      <c r="L76" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M76" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="77" spans="1:7" ht="44.1" customHeight="1">
       <c r="A77" s="4" t="s">
         <v>463</v>
       </c>
@@ -6999,18 +5608,8 @@
       <c r="G77" s="4" t="s">
         <v>511</v>
       </c>
-      <c r="H77" s="5"/>
-      <c r="I77" s="5"/>
-      <c r="J77" s="5"/>
-      <c r="K77" s="5"/>
-      <c r="L77" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M77" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="78" spans="1:7" ht="44.1" customHeight="1">
       <c r="A78" s="4" t="s">
         <v>463</v>
       </c>
@@ -7032,18 +5631,8 @@
       <c r="G78" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="H78" s="5"/>
-      <c r="I78" s="5"/>
-      <c r="J78" s="5"/>
-      <c r="K78" s="5"/>
-      <c r="L78" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M78" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="79" spans="1:7" ht="44.1" customHeight="1">
       <c r="A79" s="4" t="s">
         <v>463</v>
       </c>
@@ -7065,18 +5654,8 @@
       <c r="G79" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="H79" s="5"/>
-      <c r="I79" s="5"/>
-      <c r="J79" s="5"/>
-      <c r="K79" s="5"/>
-      <c r="L79" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M79" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="80" spans="1:7" ht="44.1" customHeight="1">
       <c r="A80" s="4" t="s">
         <v>463</v>
       </c>
@@ -7098,18 +5677,8 @@
       <c r="G80" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="H80" s="5"/>
-      <c r="I80" s="5"/>
-      <c r="J80" s="5"/>
-      <c r="K80" s="5"/>
-      <c r="L80" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M80" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="81" spans="1:7" ht="44.1" customHeight="1">
       <c r="A81" s="4" t="s">
         <v>463</v>
       </c>
@@ -7131,18 +5700,8 @@
       <c r="G81" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="H81" s="5"/>
-      <c r="I81" s="5"/>
-      <c r="J81" s="5"/>
-      <c r="K81" s="5"/>
-      <c r="L81" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M81" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="82" spans="1:7" ht="44.1" customHeight="1">
       <c r="A82" s="4" t="s">
         <v>463</v>
       </c>
@@ -7164,18 +5723,8 @@
       <c r="G82" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="H82" s="5"/>
-      <c r="I82" s="5"/>
-      <c r="J82" s="5"/>
-      <c r="K82" s="5"/>
-      <c r="L82" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M82" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="83" spans="1:7" ht="44.1" customHeight="1">
       <c r="A83" s="4" t="s">
         <v>463</v>
       </c>
@@ -7197,18 +5746,8 @@
       <c r="G83" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="H83" s="5"/>
-      <c r="I83" s="5"/>
-      <c r="J83" s="5"/>
-      <c r="K83" s="5"/>
-      <c r="L83" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M83" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="84" spans="1:7" ht="44.1" customHeight="1">
       <c r="A84" s="4" t="s">
         <v>463</v>
       </c>
@@ -7230,18 +5769,8 @@
       <c r="G84" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="H84" s="5"/>
-      <c r="I84" s="5"/>
-      <c r="J84" s="5"/>
-      <c r="K84" s="5"/>
-      <c r="L84" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M84" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="85" spans="1:7" ht="44.1" customHeight="1">
       <c r="A85" s="4" t="s">
         <v>536</v>
       </c>
@@ -7263,18 +5792,8 @@
       <c r="G85" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="H85" s="5"/>
-      <c r="I85" s="5"/>
-      <c r="J85" s="5"/>
-      <c r="K85" s="5"/>
-      <c r="L85" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M85" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="86" spans="1:7" ht="44.1" customHeight="1">
       <c r="A86" s="4" t="s">
         <v>536</v>
       </c>
@@ -7296,18 +5815,8 @@
       <c r="G86" s="4" t="s">
         <v>545</v>
       </c>
-      <c r="H86" s="5"/>
-      <c r="I86" s="5"/>
-      <c r="J86" s="5"/>
-      <c r="K86" s="5"/>
-      <c r="L86" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M86" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="87" spans="1:7" ht="44.1" customHeight="1">
       <c r="A87" s="4" t="s">
         <v>536</v>
       </c>
@@ -7329,18 +5838,8 @@
       <c r="G87" s="4" t="s">
         <v>548</v>
       </c>
-      <c r="H87" s="5"/>
-      <c r="I87" s="5"/>
-      <c r="J87" s="5"/>
-      <c r="K87" s="5"/>
-      <c r="L87" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M87" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="88" spans="1:7" ht="44.1" customHeight="1">
       <c r="A88" s="4" t="s">
         <v>536</v>
       </c>
@@ -7362,18 +5861,8 @@
       <c r="G88" s="4" t="s">
         <v>551</v>
       </c>
-      <c r="H88" s="5"/>
-      <c r="I88" s="5"/>
-      <c r="J88" s="5"/>
-      <c r="K88" s="5"/>
-      <c r="L88" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M88" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="89" spans="1:7" ht="44.1" customHeight="1">
       <c r="A89" s="4" t="s">
         <v>536</v>
       </c>
@@ -7395,18 +5884,8 @@
       <c r="G89" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="H89" s="5"/>
-      <c r="I89" s="5"/>
-      <c r="J89" s="5"/>
-      <c r="K89" s="5"/>
-      <c r="L89" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M89" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="90" spans="1:7" ht="44.1" customHeight="1">
       <c r="A90" s="4" t="s">
         <v>536</v>
       </c>
@@ -7428,18 +5907,8 @@
       <c r="G90" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="H90" s="5"/>
-      <c r="I90" s="5"/>
-      <c r="J90" s="5"/>
-      <c r="K90" s="5"/>
-      <c r="L90" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M90" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="91" spans="1:7" ht="44.1" customHeight="1">
       <c r="A91" s="4" t="s">
         <v>536</v>
       </c>
@@ -7461,18 +5930,8 @@
       <c r="G91" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="H91" s="5"/>
-      <c r="I91" s="5"/>
-      <c r="J91" s="5"/>
-      <c r="K91" s="5"/>
-      <c r="L91" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M91" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="92" spans="1:7" ht="44.1" customHeight="1">
       <c r="A92" s="4" t="s">
         <v>536</v>
       </c>
@@ -7494,18 +5953,8 @@
       <c r="G92" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="H92" s="5"/>
-      <c r="I92" s="5"/>
-      <c r="J92" s="5"/>
-      <c r="K92" s="5"/>
-      <c r="L92" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M92" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="93" spans="1:7" ht="44.1" customHeight="1">
       <c r="A93" s="4" t="s">
         <v>536</v>
       </c>
@@ -7527,18 +5976,8 @@
       <c r="G93" s="4" t="s">
         <v>569</v>
       </c>
-      <c r="H93" s="5"/>
-      <c r="I93" s="5"/>
-      <c r="J93" s="5"/>
-      <c r="K93" s="5"/>
-      <c r="L93" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M93" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="94" spans="1:7" ht="44.1" customHeight="1">
       <c r="A94" s="4" t="s">
         <v>536</v>
       </c>
@@ -7560,18 +5999,8 @@
       <c r="G94" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="H94" s="5"/>
-      <c r="I94" s="5"/>
-      <c r="J94" s="5"/>
-      <c r="K94" s="5"/>
-      <c r="L94" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M94" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="95" spans="1:7" ht="44.1" customHeight="1">
       <c r="A95" s="4" t="s">
         <v>536</v>
       </c>
@@ -7593,18 +6022,8 @@
       <c r="G95" s="4" t="s">
         <v>578</v>
       </c>
-      <c r="H95" s="5"/>
-      <c r="I95" s="5"/>
-      <c r="J95" s="5"/>
-      <c r="K95" s="5"/>
-      <c r="L95" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M95" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="96" spans="1:7" ht="44.1" customHeight="1">
       <c r="A96" s="4" t="s">
         <v>536</v>
       </c>
@@ -7626,18 +6045,8 @@
       <c r="G96" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="H96" s="5"/>
-      <c r="I96" s="5"/>
-      <c r="J96" s="5"/>
-      <c r="K96" s="5"/>
-      <c r="L96" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M96" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="97" spans="1:7" ht="44.1" customHeight="1">
       <c r="A97" s="4" t="s">
         <v>536</v>
       </c>
@@ -7659,18 +6068,8 @@
       <c r="G97" s="4" t="s">
         <v>584</v>
       </c>
-      <c r="H97" s="5"/>
-      <c r="I97" s="5"/>
-      <c r="J97" s="5"/>
-      <c r="K97" s="5"/>
-      <c r="L97" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M97" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="98" spans="1:7" ht="44.1" customHeight="1">
       <c r="A98" s="4" t="s">
         <v>536</v>
       </c>
@@ -7692,18 +6091,8 @@
       <c r="G98" s="4" t="s">
         <v>587</v>
       </c>
-      <c r="H98" s="5"/>
-      <c r="I98" s="5"/>
-      <c r="J98" s="5"/>
-      <c r="K98" s="5"/>
-      <c r="L98" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M98" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="99" spans="1:7" ht="44.1" customHeight="1">
       <c r="A99" s="4" t="s">
         <v>536</v>
       </c>
@@ -7725,18 +6114,8 @@
       <c r="G99" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="H99" s="5"/>
-      <c r="I99" s="5"/>
-      <c r="J99" s="5"/>
-      <c r="K99" s="5"/>
-      <c r="L99" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M99" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="100" spans="1:7" ht="44.1" customHeight="1">
       <c r="A100" s="4" t="s">
         <v>536</v>
       </c>
@@ -7758,18 +6137,8 @@
       <c r="G100" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="H100" s="5"/>
-      <c r="I100" s="5"/>
-      <c r="J100" s="5"/>
-      <c r="K100" s="5"/>
-      <c r="L100" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M100" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="101" spans="1:7" ht="44.1" customHeight="1">
       <c r="A101" s="4" t="s">
         <v>536</v>
       </c>
@@ -7791,18 +6160,8 @@
       <c r="G101" s="4" t="s">
         <v>599</v>
       </c>
-      <c r="H101" s="5"/>
-      <c r="I101" s="5"/>
-      <c r="J101" s="5"/>
-      <c r="K101" s="5"/>
-      <c r="L101" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M101" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="102" spans="1:7" ht="44.1" customHeight="1">
       <c r="A102" s="4" t="s">
         <v>536</v>
       </c>
@@ -7824,18 +6183,8 @@
       <c r="G102" s="4" t="s">
         <v>602</v>
       </c>
-      <c r="H102" s="5"/>
-      <c r="I102" s="5"/>
-      <c r="J102" s="5"/>
-      <c r="K102" s="5"/>
-      <c r="L102" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M102" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="103" spans="1:7" ht="44.1" customHeight="1">
       <c r="A103" s="4" t="s">
         <v>536</v>
       </c>
@@ -7857,18 +6206,8 @@
       <c r="G103" s="4" t="s">
         <v>605</v>
       </c>
-      <c r="H103" s="5"/>
-      <c r="I103" s="5"/>
-      <c r="J103" s="5"/>
-      <c r="K103" s="5"/>
-      <c r="L103" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M103" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13" ht="44.1" customHeight="1">
+    </row>
+    <row r="104" spans="1:7" ht="44.1" customHeight="1">
       <c r="A104" s="4" t="s">
         <v>536</v>
       </c>
@@ -7890,23 +6229,8 @@
       <c r="G104" s="4" t="s">
         <v>608</v>
       </c>
-      <c r="H104" s="5"/>
-      <c r="I104" s="5"/>
-      <c r="J104" s="5"/>
-      <c r="K104" s="5"/>
-      <c r="L104" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M104" s="5" t="s">
-        <v>43</v>
-      </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="M5:M104" xr:uid="{00000000-0002-0000-0300-000001000000}">
-      <formula1>"Draft,Published"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
